--- a/Datos Tesis Upstream/Algoritmos y Programacion/2526-2/Algoritmos 2526-2.xlsx
+++ b/Datos Tesis Upstream/Algoritmos y Programacion/2526-2/Algoritmos 2526-2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nelsoncarrillo/Downloads/tesis-prediccion-participacion/Datos Tesis Upstream/Algoritmos y Programacion/2526-2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{981BCC32-DAC3-7846-AFDD-1D9208BEE346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9984107F-044C-D34A-8F7A-DC0F56666158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="125">
   <si>
     <r>
       <rPr>
@@ -586,12 +586,15 @@
   <si>
     <t>Algoritmos y programación</t>
   </si>
+  <si>
+    <t>carnet</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -648,6 +651,14 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -797,7 +808,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -833,7 +844,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -848,35 +858,45 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5077,987 +5097,1142 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AB36"/>
+  <dimension ref="A1:AC36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="21.5" customWidth="1"/>
-    <col min="3" max="4" width="16" customWidth="1"/>
-    <col min="5" max="28" width="9" customWidth="1"/>
+    <col min="3" max="5" width="16" customWidth="1"/>
+    <col min="6" max="29" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="36" t="s">
+      <c r="B1" s="34" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="34" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.15">
-      <c r="A5" s="15" t="s">
+      <c r="B3" s="35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="A5" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="40" t="s">
+        <v>124</v>
+      </c>
+      <c r="F5" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="36"/>
+      <c r="H5" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15" t="s">
+      <c r="I5" s="36"/>
+      <c r="J5" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15" t="s">
+      <c r="K5" s="36"/>
+      <c r="L5" s="36" t="s">
         <v>57</v>
       </c>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15" t="s">
+      <c r="M5" s="36"/>
+      <c r="N5" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="N5" s="15"/>
-      <c r="O5" s="15" t="s">
+      <c r="O5" s="36"/>
+      <c r="P5" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="P5" s="15"/>
-      <c r="Q5" s="15" t="s">
+      <c r="Q5" s="36"/>
+      <c r="R5" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="R5" s="15"/>
-      <c r="S5" s="15" t="s">
+      <c r="S5" s="36"/>
+      <c r="T5" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="T5" s="15"/>
-      <c r="U5" s="15" t="s">
+      <c r="U5" s="36"/>
+      <c r="V5" s="36" t="s">
         <v>62</v>
       </c>
-      <c r="V5" s="15"/>
-      <c r="W5" s="15" t="s">
+      <c r="W5" s="36"/>
+      <c r="X5" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="X5" s="15"/>
-      <c r="Y5" s="15" t="s">
+      <c r="Y5" s="36"/>
+      <c r="Z5" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="Z5" s="15"/>
-      <c r="AA5" s="15" t="s">
+      <c r="AA5" s="36"/>
+      <c r="AB5" s="36" t="s">
         <v>65</v>
       </c>
-      <c r="AB5" s="15"/>
-    </row>
-    <row r="6" spans="1:28" ht="14" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="15"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="16" t="s">
+      <c r="AC5" s="36"/>
+    </row>
+    <row r="6" spans="1:29" ht="14" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="36"/>
+      <c r="B6" s="36"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="F6" s="16" t="s">
+      <c r="G6" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="G6" s="16" t="s">
+      <c r="H6" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="H6" s="16" t="s">
+      <c r="I6" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="I6" s="16" t="s">
+      <c r="J6" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="J6" s="16" t="s">
+      <c r="K6" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="K6" s="16" t="s">
+      <c r="L6" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="L6" s="16" t="s">
+      <c r="M6" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="M6" s="16" t="s">
+      <c r="N6" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="N6" s="16" t="s">
+      <c r="O6" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="O6" s="16" t="s">
+      <c r="P6" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="P6" s="16" t="s">
+      <c r="Q6" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="Q6" s="16" t="s">
+      <c r="R6" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="R6" s="16" t="s">
+      <c r="S6" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="S6" s="16" t="s">
+      <c r="T6" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="T6" s="16" t="s">
+      <c r="U6" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="U6" s="16" t="s">
+      <c r="V6" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="V6" s="16" t="s">
+      <c r="W6" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="W6" s="16" t="s">
+      <c r="X6" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="X6" s="16" t="s">
+      <c r="Y6" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="Y6" s="16" t="s">
+      <c r="Z6" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="Z6" s="16" t="s">
+      <c r="AA6" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="AA6" s="16" t="s">
+      <c r="AB6" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="AB6" s="16" t="s">
+      <c r="AC6" s="15" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="21">
-        <v>1</v>
-      </c>
-      <c r="B7" s="22" t="s">
+    <row r="7" spans="1:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="20">
+        <v>1</v>
+      </c>
+      <c r="B7" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="23">
         <v>32535007</v>
       </c>
-      <c r="E7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="I7" s="17"/>
-      <c r="K7" s="17">
+      <c r="E7" s="37" t="inlineStr">
+        <is>
+          <t>20261110204</t>
+        </is>
+      </c>
+      <c r="F7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="J7" s="16"/>
+      <c r="L7" s="16">
         <v>4</v>
       </c>
-      <c r="M7" s="17"/>
-      <c r="N7" s="30"/>
-      <c r="O7" s="32"/>
-      <c r="P7">
-        <v>1</v>
-      </c>
-      <c r="U7" s="17"/>
-      <c r="Y7" s="17"/>
-    </row>
-    <row r="8" spans="1:28" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="21">
+      <c r="N7" s="16"/>
+      <c r="O7" s="28"/>
+      <c r="P7" s="30"/>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="V7" s="16"/>
+      <c r="Z7" s="16"/>
+    </row>
+    <row r="8" spans="1:29" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="20">
         <v>2</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="25">
         <v>32753793</v>
       </c>
-      <c r="E8" s="18"/>
-      <c r="G8" s="19"/>
-      <c r="I8" s="18"/>
-      <c r="K8" s="18"/>
-      <c r="M8" s="18"/>
-      <c r="N8" s="30"/>
-      <c r="O8" s="33"/>
-      <c r="U8" s="18"/>
-      <c r="Y8" s="18"/>
-    </row>
-    <row r="9" spans="1:28" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="21">
+      <c r="E8" s="38" t="inlineStr">
+        <is>
+          <t>20261110278</t>
+        </is>
+      </c>
+      <c r="F8" s="17"/>
+      <c r="H8" s="18"/>
+      <c r="J8" s="17"/>
+      <c r="L8" s="17"/>
+      <c r="N8" s="17"/>
+      <c r="O8" s="28"/>
+      <c r="P8" s="31"/>
+      <c r="V8" s="17"/>
+      <c r="Z8" s="17"/>
+    </row>
+    <row r="9" spans="1:29" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="20">
         <v>3</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C9" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="25">
         <v>32473285</v>
       </c>
-      <c r="E9" s="17"/>
-      <c r="G9" s="20"/>
-      <c r="I9" s="17"/>
-      <c r="K9" s="17"/>
-      <c r="M9" s="17"/>
-      <c r="N9" s="30"/>
-      <c r="O9" s="32"/>
-      <c r="U9" s="17">
-        <v>1</v>
-      </c>
-      <c r="Y9" s="17"/>
-    </row>
-    <row r="10" spans="1:28" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="21">
+      <c r="E9" s="38" t="inlineStr">
+        <is>
+          <t>20261110523</t>
+        </is>
+      </c>
+      <c r="F9" s="16"/>
+      <c r="H9" s="19"/>
+      <c r="J9" s="16"/>
+      <c r="L9" s="16"/>
+      <c r="N9" s="16"/>
+      <c r="O9" s="28"/>
+      <c r="P9" s="30"/>
+      <c r="V9" s="16">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="16"/>
+    </row>
+    <row r="10" spans="1:29" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="20">
         <v>4</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="C10" s="27" t="s">
+      <c r="C10" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="25">
         <v>32235603</v>
       </c>
-      <c r="E10" s="18"/>
-      <c r="G10" s="18"/>
-      <c r="I10" s="19"/>
-      <c r="K10" s="18"/>
-      <c r="M10" s="18"/>
-      <c r="N10" s="30"/>
-      <c r="O10" s="33"/>
-      <c r="U10" s="18"/>
-      <c r="Y10" s="18"/>
-    </row>
-    <row r="11" spans="1:28" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="21">
+      <c r="E10" s="38" t="inlineStr">
+        <is>
+          <t>20261110725</t>
+        </is>
+      </c>
+      <c r="F10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="J10" s="18"/>
+      <c r="L10" s="17"/>
+      <c r="N10" s="17"/>
+      <c r="O10" s="28"/>
+      <c r="P10" s="31"/>
+      <c r="V10" s="17"/>
+      <c r="Z10" s="17"/>
+    </row>
+    <row r="11" spans="1:29" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="20">
         <v>5</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="C11" s="27" t="s">
+      <c r="C11" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="25">
         <v>32749893</v>
       </c>
-      <c r="E11" s="17"/>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11" s="17"/>
-      <c r="I11" s="17"/>
-      <c r="K11" s="17"/>
-      <c r="M11" s="17">
-        <v>1</v>
-      </c>
-      <c r="N11" s="30"/>
-      <c r="O11" s="32"/>
-      <c r="U11" s="17"/>
-      <c r="Y11" s="17"/>
-    </row>
-    <row r="12" spans="1:28" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="21">
+      <c r="E11" s="38" t="inlineStr">
+        <is>
+          <t>20261110557</t>
+        </is>
+      </c>
+      <c r="F11" s="16"/>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11" s="16"/>
+      <c r="J11" s="16"/>
+      <c r="L11" s="16"/>
+      <c r="N11" s="16">
+        <v>1</v>
+      </c>
+      <c r="O11" s="28"/>
+      <c r="P11" s="30"/>
+      <c r="V11" s="16"/>
+      <c r="Z11" s="16"/>
+    </row>
+    <row r="12" spans="1:29" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="20">
         <v>6</v>
       </c>
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="C12" s="27" t="s">
+      <c r="C12" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="25">
         <v>32227280</v>
       </c>
-      <c r="E12" s="18"/>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="G12" s="18"/>
-      <c r="I12" s="18"/>
-      <c r="K12" s="18"/>
-      <c r="M12" s="18"/>
-      <c r="N12" s="30"/>
-      <c r="O12" s="33"/>
-      <c r="U12" s="18">
-        <v>1</v>
-      </c>
-      <c r="Y12" s="18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:28" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="21">
+      <c r="E12" s="38" t="inlineStr">
+        <is>
+          <t>20261110373</t>
+        </is>
+      </c>
+      <c r="F12" s="17"/>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12" s="17"/>
+      <c r="J12" s="17"/>
+      <c r="L12" s="17"/>
+      <c r="N12" s="17"/>
+      <c r="O12" s="28"/>
+      <c r="P12" s="31"/>
+      <c r="V12" s="17">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="20">
         <v>7</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="C13" s="27" t="s">
+      <c r="C13" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="25">
         <v>31821320</v>
       </c>
-      <c r="E13" s="17">
-        <v>1</v>
-      </c>
-      <c r="G13" s="17"/>
-      <c r="I13" s="20">
+      <c r="E13" s="38" t="inlineStr">
+        <is>
+          <t>20261110394</t>
+        </is>
+      </c>
+      <c r="F13" s="16">
+        <v>1</v>
+      </c>
+      <c r="H13" s="16"/>
+      <c r="J13" s="19">
         <v>2</v>
       </c>
-      <c r="K13" s="17">
+      <c r="L13" s="16">
         <v>2</v>
       </c>
-      <c r="L13">
-        <v>1</v>
-      </c>
-      <c r="M13" s="17">
-        <v>1</v>
-      </c>
-      <c r="N13" s="30"/>
-      <c r="O13" s="32"/>
-      <c r="P13" s="31">
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13" s="16">
+        <v>1</v>
+      </c>
+      <c r="O13" s="28"/>
+      <c r="P13" s="30"/>
+      <c r="Q13" s="29">
         <v>3</v>
       </c>
-      <c r="U13" s="17"/>
-      <c r="Y13" s="17"/>
-    </row>
-    <row r="14" spans="1:28" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="21">
+      <c r="V13" s="16"/>
+      <c r="Z13" s="16"/>
+    </row>
+    <row r="14" spans="1:29" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="20">
         <v>8</v>
       </c>
-      <c r="B14" s="25" t="s">
+      <c r="B14" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="C14" s="27" t="s">
+      <c r="C14" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="25">
         <v>36064964</v>
       </c>
-      <c r="E14" s="19">
-        <v>1</v>
-      </c>
-      <c r="G14" s="18"/>
-      <c r="I14" s="18"/>
-      <c r="K14" s="18"/>
-      <c r="M14" s="18"/>
-      <c r="N14" s="30"/>
-      <c r="O14" s="33"/>
-      <c r="U14" s="18"/>
-      <c r="Y14" s="18"/>
-    </row>
-    <row r="15" spans="1:28" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="21">
+      <c r="E14" s="38" t="inlineStr">
+        <is>
+          <t>20261110163</t>
+        </is>
+      </c>
+      <c r="F14" s="18">
+        <v>1</v>
+      </c>
+      <c r="H14" s="17"/>
+      <c r="J14" s="17"/>
+      <c r="L14" s="17"/>
+      <c r="N14" s="17"/>
+      <c r="O14" s="28"/>
+      <c r="P14" s="31"/>
+      <c r="V14" s="17"/>
+      <c r="Z14" s="17"/>
+    </row>
+    <row r="15" spans="1:29" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="20">
         <v>9</v>
       </c>
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="C15" s="27" t="s">
+      <c r="C15" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="25">
         <v>32357635</v>
       </c>
-      <c r="E15" s="17"/>
-      <c r="G15" s="17"/>
-      <c r="I15" s="17"/>
-      <c r="K15" s="17"/>
-      <c r="M15" s="17"/>
-      <c r="N15" s="30"/>
-      <c r="O15" s="32"/>
-      <c r="U15" s="17"/>
-      <c r="Y15" s="17"/>
-    </row>
-    <row r="16" spans="1:28" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="21">
+      <c r="E15" s="38" t="inlineStr">
+        <is>
+          <t>20251130204</t>
+        </is>
+      </c>
+      <c r="F15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="J15" s="16"/>
+      <c r="L15" s="16"/>
+      <c r="N15" s="16"/>
+      <c r="O15" s="28"/>
+      <c r="P15" s="30"/>
+      <c r="V15" s="16"/>
+      <c r="Z15" s="16"/>
+    </row>
+    <row r="16" spans="1:29" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="20">
         <v>10</v>
       </c>
-      <c r="B16" s="25" t="s">
+      <c r="B16" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="C16" s="27" t="s">
+      <c r="C16" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="D16" s="26">
+      <c r="D16" s="25">
         <v>30538964</v>
       </c>
-      <c r="E16" s="18"/>
-      <c r="G16" s="18"/>
-      <c r="I16" s="19"/>
-      <c r="K16" s="18">
-        <v>1</v>
-      </c>
-      <c r="M16" s="18"/>
-      <c r="N16" s="30"/>
-      <c r="O16" s="33"/>
-      <c r="U16" s="18"/>
-      <c r="Y16" s="18"/>
-      <c r="Z16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:26" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="21">
+      <c r="E16" s="38" t="inlineStr">
+        <is>
+          <t>20261110267</t>
+        </is>
+      </c>
+      <c r="F16" s="17"/>
+      <c r="H16" s="17"/>
+      <c r="J16" s="18"/>
+      <c r="L16" s="17">
+        <v>1</v>
+      </c>
+      <c r="N16" s="17"/>
+      <c r="O16" s="28"/>
+      <c r="P16" s="31"/>
+      <c r="V16" s="17"/>
+      <c r="Z16" s="17"/>
+      <c r="AA16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="20">
         <v>11</v>
       </c>
-      <c r="B17" s="22" t="s">
+      <c r="B17" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="C17" s="27" t="s">
+      <c r="C17" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="D17" s="26">
+      <c r="D17" s="25">
         <v>32348335</v>
       </c>
-      <c r="E17" s="17">
-        <v>1</v>
-      </c>
-      <c r="G17" s="17"/>
-      <c r="I17" s="17"/>
-      <c r="K17" s="17"/>
-      <c r="M17" s="17"/>
-      <c r="N17" s="30"/>
-      <c r="O17" s="32"/>
-      <c r="U17" s="17"/>
-      <c r="Y17" s="17"/>
-    </row>
-    <row r="18" spans="1:26" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="21">
+      <c r="E17" s="38" t="inlineStr">
+        <is>
+          <t>20261110006</t>
+        </is>
+      </c>
+      <c r="F17" s="16">
+        <v>1</v>
+      </c>
+      <c r="H17" s="16"/>
+      <c r="J17" s="16"/>
+      <c r="L17" s="16"/>
+      <c r="N17" s="16"/>
+      <c r="O17" s="28"/>
+      <c r="P17" s="30"/>
+      <c r="V17" s="16"/>
+      <c r="Z17" s="16"/>
+    </row>
+    <row r="18" spans="1:27" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="20">
         <v>12</v>
       </c>
-      <c r="B18" s="25" t="s">
+      <c r="B18" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="C18" s="27" t="s">
+      <c r="C18" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="D18" s="26">
+      <c r="D18" s="25">
         <v>32122169</v>
       </c>
-      <c r="E18" s="18"/>
-      <c r="G18" s="18"/>
-      <c r="I18" s="18"/>
-      <c r="K18" s="18"/>
-      <c r="M18" s="18"/>
-      <c r="N18" s="30"/>
-      <c r="O18" s="33"/>
-      <c r="U18" s="18"/>
-      <c r="Y18" s="18"/>
-    </row>
-    <row r="19" spans="1:26" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="21">
+      <c r="E18" s="38" t="inlineStr">
+        <is>
+          <t>20241130204</t>
+        </is>
+      </c>
+      <c r="F18" s="17"/>
+      <c r="H18" s="17"/>
+      <c r="J18" s="17"/>
+      <c r="L18" s="17"/>
+      <c r="N18" s="17"/>
+      <c r="O18" s="28"/>
+      <c r="P18" s="31"/>
+      <c r="V18" s="17"/>
+      <c r="Z18" s="17"/>
+    </row>
+    <row r="19" spans="1:27" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="20">
         <v>13</v>
       </c>
-      <c r="B19" s="22" t="s">
+      <c r="B19" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="C19" s="27" t="s">
+      <c r="C19" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="D19" s="26">
+      <c r="D19" s="25">
         <v>32013622</v>
       </c>
-      <c r="E19" s="17">
-        <v>1</v>
-      </c>
-      <c r="G19" s="20"/>
-      <c r="I19" s="20"/>
-      <c r="K19" s="17"/>
-      <c r="M19" s="17"/>
-      <c r="N19" s="30"/>
-      <c r="O19" s="32"/>
-      <c r="U19" s="17"/>
-      <c r="Y19" s="17"/>
-    </row>
-    <row r="20" spans="1:26" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="21">
+      <c r="E19" s="38" t="inlineStr">
+        <is>
+          <t>20251110490</t>
+        </is>
+      </c>
+      <c r="F19" s="16">
+        <v>1</v>
+      </c>
+      <c r="H19" s="19"/>
+      <c r="J19" s="19"/>
+      <c r="L19" s="16"/>
+      <c r="N19" s="16"/>
+      <c r="O19" s="28"/>
+      <c r="P19" s="30"/>
+      <c r="V19" s="16"/>
+      <c r="Z19" s="16"/>
+    </row>
+    <row r="20" spans="1:27" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="20">
         <v>14</v>
       </c>
-      <c r="B20" s="25" t="s">
+      <c r="B20" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="C20" s="27" t="s">
+      <c r="C20" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="D20" s="26">
+      <c r="D20" s="25">
         <v>30497178</v>
       </c>
-      <c r="E20" s="18"/>
-      <c r="F20">
-        <v>1</v>
-      </c>
-      <c r="G20" s="19"/>
-      <c r="I20" s="18"/>
-      <c r="K20" s="18"/>
-      <c r="M20" s="18"/>
-      <c r="N20" s="30"/>
-      <c r="O20" s="33"/>
-      <c r="U20" s="18"/>
-      <c r="Y20" s="18"/>
-    </row>
-    <row r="21" spans="1:26" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="21">
+      <c r="E20" s="38" t="inlineStr">
+        <is>
+          <t>20251130073</t>
+        </is>
+      </c>
+      <c r="F20" s="17"/>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20" s="18"/>
+      <c r="J20" s="17"/>
+      <c r="L20" s="17"/>
+      <c r="N20" s="17"/>
+      <c r="O20" s="28"/>
+      <c r="P20" s="31"/>
+      <c r="V20" s="17"/>
+      <c r="Z20" s="17"/>
+    </row>
+    <row r="21" spans="1:27" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="20">
         <v>15</v>
       </c>
-      <c r="B21" s="22" t="s">
+      <c r="B21" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="C21" s="27" t="s">
+      <c r="C21" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="D21" s="26">
+      <c r="D21" s="25">
         <v>32337077</v>
       </c>
-      <c r="E21" s="17"/>
-      <c r="G21" s="20"/>
-      <c r="I21" s="20"/>
-      <c r="K21" s="17"/>
-      <c r="M21" s="20"/>
-      <c r="N21" s="30"/>
-      <c r="O21" s="34"/>
-      <c r="U21" s="17"/>
-      <c r="Y21" s="17"/>
-    </row>
-    <row r="22" spans="1:26" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="21">
+      <c r="E21" s="38" t="inlineStr">
+        <is>
+          <t>20261110126</t>
+        </is>
+      </c>
+      <c r="F21" s="16"/>
+      <c r="H21" s="19"/>
+      <c r="J21" s="19"/>
+      <c r="L21" s="16"/>
+      <c r="N21" s="19"/>
+      <c r="O21" s="28"/>
+      <c r="P21" s="32"/>
+      <c r="V21" s="16"/>
+      <c r="Z21" s="16"/>
+    </row>
+    <row r="22" spans="1:27" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="20">
         <v>16</v>
       </c>
-      <c r="B22" s="25" t="s">
+      <c r="B22" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="C22" s="27" t="s">
+      <c r="C22" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="D22" s="26">
+      <c r="D22" s="25">
         <v>32348512</v>
       </c>
-      <c r="E22" s="18">
-        <v>1</v>
-      </c>
-      <c r="G22" s="18"/>
-      <c r="I22" s="19"/>
-      <c r="K22" s="18"/>
-      <c r="M22" s="19"/>
-      <c r="N22" s="30"/>
-      <c r="O22" s="33"/>
-      <c r="U22" s="18">
-        <v>1</v>
-      </c>
-      <c r="Y22" s="18"/>
-    </row>
-    <row r="23" spans="1:26" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="21">
+      <c r="E22" s="38" t="inlineStr">
+        <is>
+          <t>20261110130</t>
+        </is>
+      </c>
+      <c r="F22" s="17">
+        <v>1</v>
+      </c>
+      <c r="H22" s="17"/>
+      <c r="J22" s="18"/>
+      <c r="L22" s="17"/>
+      <c r="N22" s="18"/>
+      <c r="O22" s="28"/>
+      <c r="P22" s="31"/>
+      <c r="V22" s="17">
+        <v>1</v>
+      </c>
+      <c r="Z22" s="17"/>
+    </row>
+    <row r="23" spans="1:27" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="20">
         <v>17</v>
       </c>
-      <c r="B23" s="22" t="s">
+      <c r="B23" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="C23" s="27" t="s">
+      <c r="C23" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="D23" s="26">
+      <c r="D23" s="25">
         <v>32226530</v>
       </c>
-      <c r="E23" s="17">
-        <v>1</v>
-      </c>
-      <c r="G23" s="20"/>
-      <c r="I23" s="20">
+      <c r="E23" s="38" t="inlineStr">
+        <is>
+          <t>20261110202</t>
+        </is>
+      </c>
+      <c r="F23" s="16">
+        <v>1</v>
+      </c>
+      <c r="H23" s="19"/>
+      <c r="J23" s="19">
         <v>2</v>
       </c>
-      <c r="J23">
-        <v>1</v>
-      </c>
-      <c r="K23" s="17"/>
-      <c r="M23" s="17"/>
-      <c r="N23" s="30"/>
-      <c r="O23" s="32"/>
-      <c r="U23" s="17"/>
-      <c r="Y23" s="17"/>
-    </row>
-    <row r="24" spans="1:26" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="21">
+      <c r="K23">
+        <v>1</v>
+      </c>
+      <c r="L23" s="16"/>
+      <c r="N23" s="16"/>
+      <c r="O23" s="28"/>
+      <c r="P23" s="30"/>
+      <c r="V23" s="16"/>
+      <c r="Z23" s="16"/>
+    </row>
+    <row r="24" spans="1:27" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="20">
         <v>18</v>
       </c>
-      <c r="B24" s="25" t="s">
+      <c r="B24" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="C24" s="27" t="s">
+      <c r="C24" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="D24" s="26">
+      <c r="D24" s="25">
         <v>31873764</v>
       </c>
-      <c r="E24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="I24" s="18"/>
-      <c r="J24">
-        <v>1</v>
-      </c>
-      <c r="K24" s="18">
-        <v>1</v>
-      </c>
-      <c r="L24">
+      <c r="E24" s="38" t="inlineStr">
+        <is>
+          <t>20251110157</t>
+        </is>
+      </c>
+      <c r="F24" s="17"/>
+      <c r="H24" s="17"/>
+      <c r="J24" s="17"/>
+      <c r="K24">
+        <v>1</v>
+      </c>
+      <c r="L24" s="17">
+        <v>1</v>
+      </c>
+      <c r="M24">
         <v>3</v>
       </c>
-      <c r="M24" s="18"/>
-      <c r="N24" s="30"/>
-      <c r="O24" s="33"/>
-      <c r="U24" s="18"/>
-      <c r="Y24" s="18"/>
-    </row>
-    <row r="25" spans="1:26" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="21">
+      <c r="N24" s="17"/>
+      <c r="O24" s="28"/>
+      <c r="P24" s="31"/>
+      <c r="V24" s="17"/>
+      <c r="Z24" s="17"/>
+    </row>
+    <row r="25" spans="1:27" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="20">
         <v>19</v>
       </c>
-      <c r="B25" s="22" t="s">
+      <c r="B25" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="C25" s="27" t="s">
+      <c r="C25" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="D25" s="26">
+      <c r="D25" s="25">
         <v>32396833</v>
       </c>
-      <c r="E25" s="17"/>
-      <c r="G25" s="17"/>
-      <c r="I25" s="17"/>
-      <c r="K25" s="17"/>
-      <c r="M25" s="17"/>
-      <c r="N25" s="30"/>
-      <c r="O25" s="32"/>
-      <c r="U25" s="17"/>
-      <c r="Y25" s="17"/>
-      <c r="Z25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:26" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="21">
+      <c r="E25" s="38" t="inlineStr">
+        <is>
+          <t>20261110444</t>
+        </is>
+      </c>
+      <c r="F25" s="16"/>
+      <c r="H25" s="16"/>
+      <c r="J25" s="16"/>
+      <c r="L25" s="16"/>
+      <c r="N25" s="16"/>
+      <c r="O25" s="28"/>
+      <c r="P25" s="30"/>
+      <c r="V25" s="16"/>
+      <c r="Z25" s="16"/>
+      <c r="AA25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="20">
         <v>20</v>
       </c>
-      <c r="B26" s="25" t="s">
+      <c r="B26" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="C26" s="27" t="s">
+      <c r="C26" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="D26" s="26">
+      <c r="D26" s="25">
         <v>32292306</v>
       </c>
-      <c r="E26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="I26" s="18"/>
-      <c r="K26" s="18">
-        <v>1</v>
-      </c>
-      <c r="M26" s="18"/>
-      <c r="N26" s="30"/>
-      <c r="O26" s="33"/>
-      <c r="U26" s="18"/>
-      <c r="Y26" s="18"/>
-      <c r="Z26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:26" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="21">
+      <c r="E26" s="38" t="inlineStr">
+        <is>
+          <t>20261110337</t>
+        </is>
+      </c>
+      <c r="F26" s="17"/>
+      <c r="H26" s="17"/>
+      <c r="J26" s="17"/>
+      <c r="L26" s="17">
+        <v>1</v>
+      </c>
+      <c r="N26" s="17"/>
+      <c r="O26" s="28"/>
+      <c r="P26" s="31"/>
+      <c r="V26" s="17"/>
+      <c r="Z26" s="17"/>
+      <c r="AA26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="20">
         <v>21</v>
       </c>
-      <c r="B27" s="22" t="s">
+      <c r="B27" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="C27" s="23" t="s">
+      <c r="C27" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="D27" s="26">
+      <c r="D27" s="25">
         <v>31873213</v>
       </c>
-      <c r="E27" s="17"/>
-      <c r="G27" s="17"/>
-      <c r="I27" s="17"/>
-      <c r="K27" s="17"/>
-      <c r="M27" s="17"/>
-      <c r="N27" s="30"/>
-      <c r="O27" s="32"/>
-      <c r="U27" s="17"/>
-      <c r="Y27" s="17"/>
-    </row>
-    <row r="28" spans="1:26" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="21">
+      <c r="E27" s="38" t="inlineStr">
+        <is>
+          <t>20241110461</t>
+        </is>
+      </c>
+      <c r="F27" s="16"/>
+      <c r="H27" s="16"/>
+      <c r="J27" s="16"/>
+      <c r="L27" s="16"/>
+      <c r="N27" s="16"/>
+      <c r="O27" s="28"/>
+      <c r="P27" s="30"/>
+      <c r="V27" s="16"/>
+      <c r="Z27" s="16"/>
+    </row>
+    <row r="28" spans="1:27" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="20">
         <v>22</v>
       </c>
-      <c r="B28" s="25" t="s">
+      <c r="B28" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="C28" s="23" t="s">
+      <c r="C28" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="D28" s="26">
+      <c r="D28" s="25">
         <v>32520003</v>
       </c>
-      <c r="E28" s="18">
-        <v>1</v>
-      </c>
-      <c r="F28">
-        <v>1</v>
-      </c>
-      <c r="G28" s="19"/>
-      <c r="I28" s="19"/>
-      <c r="K28" s="18"/>
-      <c r="M28" s="19"/>
-      <c r="N28" s="30"/>
-      <c r="O28" s="35"/>
-      <c r="U28" s="18"/>
-      <c r="Y28" s="18"/>
-    </row>
-    <row r="29" spans="1:26" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="21">
+      <c r="E28" s="38" t="inlineStr">
+        <is>
+          <t>20261110687</t>
+        </is>
+      </c>
+      <c r="F28" s="17">
+        <v>1</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="H28" s="18"/>
+      <c r="J28" s="18"/>
+      <c r="L28" s="17"/>
+      <c r="N28" s="18"/>
+      <c r="O28" s="28"/>
+      <c r="P28" s="33"/>
+      <c r="V28" s="17"/>
+      <c r="Z28" s="17"/>
+    </row>
+    <row r="29" spans="1:27" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="20">
         <v>23</v>
       </c>
-      <c r="B29" s="22" t="s">
+      <c r="B29" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="C29" s="23" t="s">
+      <c r="C29" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="D29" s="26">
+      <c r="D29" s="25">
         <v>34002480</v>
       </c>
-      <c r="E29" s="17"/>
-      <c r="G29" s="17"/>
-      <c r="I29" s="17"/>
-      <c r="K29" s="17"/>
-      <c r="M29" s="17"/>
-      <c r="N29" s="30"/>
-      <c r="O29" s="32"/>
-      <c r="U29" s="17"/>
-      <c r="Y29" s="17"/>
-    </row>
-    <row r="30" spans="1:26" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="21">
+      <c r="E29" s="38" t="inlineStr">
+        <is>
+          <t>20261110653</t>
+        </is>
+      </c>
+      <c r="F29" s="16"/>
+      <c r="H29" s="16"/>
+      <c r="J29" s="16"/>
+      <c r="L29" s="16"/>
+      <c r="N29" s="16"/>
+      <c r="O29" s="28"/>
+      <c r="P29" s="30"/>
+      <c r="V29" s="16"/>
+      <c r="Z29" s="16"/>
+    </row>
+    <row r="30" spans="1:27" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="20">
         <v>24</v>
       </c>
-      <c r="B30" s="25" t="s">
+      <c r="B30" s="24" t="s">
         <v>108</v>
       </c>
-      <c r="C30" s="23" t="s">
+      <c r="C30" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="D30" s="26">
+      <c r="D30" s="25">
         <v>32122247</v>
       </c>
-      <c r="E30" s="18"/>
-      <c r="G30" s="18"/>
-      <c r="I30" s="18">
-        <v>1</v>
-      </c>
-      <c r="K30" s="18"/>
-      <c r="M30" s="18"/>
-      <c r="N30" s="30"/>
-      <c r="O30" s="33"/>
-      <c r="U30" s="18"/>
-      <c r="Y30" s="18"/>
-    </row>
-    <row r="31" spans="1:26" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="21">
+      <c r="E30" s="38" t="inlineStr">
+        <is>
+          <t>20261110499</t>
+        </is>
+      </c>
+      <c r="F30" s="17"/>
+      <c r="H30" s="17"/>
+      <c r="J30" s="17">
+        <v>1</v>
+      </c>
+      <c r="L30" s="17"/>
+      <c r="N30" s="17"/>
+      <c r="O30" s="28"/>
+      <c r="P30" s="31"/>
+      <c r="V30" s="17"/>
+      <c r="Z30" s="17"/>
+    </row>
+    <row r="31" spans="1:27" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="20">
         <v>25</v>
       </c>
-      <c r="B31" s="22" t="s">
+      <c r="B31" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="C31" s="23" t="s">
+      <c r="C31" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="D31" s="26">
+      <c r="D31" s="25">
         <v>32857188</v>
       </c>
-      <c r="E31" s="17">
-        <v>1</v>
-      </c>
-      <c r="G31" s="17"/>
-      <c r="I31" s="17">
+      <c r="E31" s="38" t="inlineStr">
+        <is>
+          <t>20261110259</t>
+        </is>
+      </c>
+      <c r="F31" s="16">
+        <v>1</v>
+      </c>
+      <c r="H31" s="16"/>
+      <c r="J31" s="16">
         <v>3</v>
       </c>
-      <c r="K31" s="17"/>
-      <c r="M31" s="17"/>
-      <c r="N31" s="30"/>
-      <c r="O31" s="32"/>
-      <c r="U31" s="17">
-        <v>1</v>
-      </c>
-      <c r="Y31" s="17"/>
-    </row>
-    <row r="32" spans="1:26" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="21">
+      <c r="L31" s="16"/>
+      <c r="N31" s="16"/>
+      <c r="O31" s="28"/>
+      <c r="P31" s="30"/>
+      <c r="V31" s="16">
+        <v>1</v>
+      </c>
+      <c r="Z31" s="16"/>
+    </row>
+    <row r="32" spans="1:27" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="20">
         <v>26</v>
       </c>
-      <c r="B32" s="25" t="s">
+      <c r="B32" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="C32" s="23" t="s">
+      <c r="C32" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="D32" s="26">
+      <c r="D32" s="25">
         <v>32624143</v>
       </c>
-      <c r="E32" s="18"/>
-      <c r="F32">
-        <v>1</v>
-      </c>
-      <c r="G32" s="18"/>
-      <c r="I32" s="18">
+      <c r="E32" s="38" t="inlineStr">
+        <is>
+          <t>20261110294</t>
+        </is>
+      </c>
+      <c r="F32" s="17"/>
+      <c r="G32">
+        <v>1</v>
+      </c>
+      <c r="H32" s="17"/>
+      <c r="J32" s="17">
         <v>2</v>
       </c>
-      <c r="K32" s="18"/>
-      <c r="M32" s="18"/>
-      <c r="N32" s="30"/>
-      <c r="O32" s="33"/>
-      <c r="U32" s="18">
-        <v>1</v>
-      </c>
-      <c r="Y32" s="18"/>
-    </row>
-    <row r="33" spans="1:25" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="21">
+      <c r="L32" s="17"/>
+      <c r="N32" s="17"/>
+      <c r="O32" s="28"/>
+      <c r="P32" s="31"/>
+      <c r="V32" s="17">
+        <v>1</v>
+      </c>
+      <c r="Z32" s="17"/>
+    </row>
+    <row r="33" spans="1:26" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="20">
         <v>27</v>
       </c>
-      <c r="B33" s="28" t="s">
+      <c r="B33" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="C33" s="23" t="s">
+      <c r="C33" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="D33" s="26">
+      <c r="D33" s="25">
         <v>32504495</v>
       </c>
-      <c r="E33" s="17">
-        <v>1</v>
-      </c>
-      <c r="G33" s="17"/>
-      <c r="I33" s="17">
+      <c r="E33" s="38" t="inlineStr">
+        <is>
+          <t>20261110285</t>
+        </is>
+      </c>
+      <c r="F33" s="16">
+        <v>1</v>
+      </c>
+      <c r="H33" s="16"/>
+      <c r="J33" s="16">
         <v>3</v>
       </c>
-      <c r="K33" s="17"/>
-      <c r="M33" s="17"/>
-      <c r="N33" s="30"/>
-      <c r="O33" s="32"/>
-      <c r="U33" s="17">
-        <v>1</v>
-      </c>
-      <c r="Y33" s="17"/>
-    </row>
-    <row r="34" spans="1:25" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="21">
+      <c r="L33" s="16"/>
+      <c r="N33" s="16"/>
+      <c r="O33" s="28"/>
+      <c r="P33" s="30"/>
+      <c r="V33" s="16">
+        <v>1</v>
+      </c>
+      <c r="Z33" s="16"/>
+    </row>
+    <row r="34" spans="1:26" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="20">
         <v>28</v>
       </c>
-      <c r="B34" s="28" t="s">
+      <c r="B34" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="C34" s="23" t="s">
+      <c r="C34" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="D34" s="26">
+      <c r="D34" s="25">
         <v>32538098</v>
       </c>
-      <c r="E34" s="18"/>
-      <c r="G34" s="18"/>
-      <c r="I34" s="18"/>
-      <c r="K34" s="18"/>
-      <c r="M34" s="18"/>
-      <c r="N34" s="30"/>
-      <c r="O34" s="33"/>
-      <c r="U34" s="18"/>
-      <c r="Y34" s="18"/>
-    </row>
-    <row r="35" spans="1:25" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="21">
+      <c r="E34" s="38" t="inlineStr">
+        <is>
+          <t>20261110623</t>
+        </is>
+      </c>
+      <c r="F34" s="17"/>
+      <c r="H34" s="17"/>
+      <c r="J34" s="17"/>
+      <c r="L34" s="17"/>
+      <c r="N34" s="17"/>
+      <c r="O34" s="28"/>
+      <c r="P34" s="31"/>
+      <c r="V34" s="17"/>
+      <c r="Z34" s="17"/>
+    </row>
+    <row r="35" spans="1:26" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="20">
         <v>29</v>
       </c>
-      <c r="B35" s="28" t="s">
+      <c r="B35" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="C35" s="23" t="s">
+      <c r="C35" s="22" t="s">
         <v>118</v>
       </c>
-      <c r="D35" s="26">
+      <c r="D35" s="25">
         <v>32110956</v>
       </c>
-      <c r="E35" s="17"/>
-      <c r="G35" s="17"/>
-      <c r="I35" s="17"/>
-      <c r="K35" s="17"/>
-      <c r="M35" s="17"/>
-      <c r="N35" s="30"/>
-      <c r="O35" s="32"/>
-      <c r="U35" s="17"/>
-      <c r="Y35" s="17"/>
-    </row>
-    <row r="36" spans="1:25" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="21">
+      <c r="E35" s="38" t="inlineStr">
+        <is>
+          <t>20261110092</t>
+        </is>
+      </c>
+      <c r="F35" s="16"/>
+      <c r="H35" s="16"/>
+      <c r="J35" s="16"/>
+      <c r="L35" s="16"/>
+      <c r="N35" s="16"/>
+      <c r="O35" s="28"/>
+      <c r="P35" s="30"/>
+      <c r="V35" s="16"/>
+      <c r="Z35" s="16"/>
+    </row>
+    <row r="36" spans="1:26" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="20">
         <v>30</v>
       </c>
-      <c r="B36" s="28" t="s">
+      <c r="B36" s="26" t="s">
         <v>113</v>
       </c>
-      <c r="C36" s="23" t="s">
+      <c r="C36" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="D36" s="29">
+      <c r="D36" s="27">
         <v>30774515</v>
       </c>
-      <c r="E36" s="18"/>
-      <c r="G36" s="18"/>
-      <c r="I36" s="18"/>
-      <c r="K36" s="18"/>
-      <c r="M36" s="18"/>
-      <c r="N36" s="30"/>
-      <c r="O36" s="33"/>
-      <c r="U36" s="18"/>
-      <c r="Y36" s="18"/>
+      <c r="E36" s="38" t="inlineStr">
+        <is>
+          <t>20251130180</t>
+        </is>
+      </c>
+      <c r="F36" s="17"/>
+      <c r="H36" s="17"/>
+      <c r="J36" s="17"/>
+      <c r="L36" s="17"/>
+      <c r="N36" s="17"/>
+      <c r="O36" s="28"/>
+      <c r="P36" s="31"/>
+      <c r="V36" s="17"/>
+      <c r="Z36" s="17"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="AA5:AB5"/>
-    <mergeCell ref="Q5:R5"/>
-    <mergeCell ref="S5:T5"/>
-    <mergeCell ref="U5:V5"/>
-    <mergeCell ref="W5:X5"/>
-    <mergeCell ref="Y5:Z5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="O5:P5"/>
+  <mergeCells count="17">
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="AB5:AC5"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="T5:U5"/>
+    <mergeCell ref="V5:W5"/>
+    <mergeCell ref="X5:Y5"/>
+    <mergeCell ref="Z5:AA5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Datos Tesis Upstream/Algoritmos y Programacion/2526-2/Algoritmos 2526-2.xlsx
+++ b/Datos Tesis Upstream/Algoritmos y Programacion/2526-2/Algoritmos 2526-2.xlsx
@@ -15,6 +15,7 @@
   <sheets>
     <sheet name="ALGORITMOS" sheetId="1" r:id="rId1"/>
     <sheet name="Estandar" sheetId="2" r:id="rId2"/>
+    <sheet name="Cronograma" sheetId="3" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -5274,233 +5275,229 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="20">
         <v>1</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="D7" s="23">
-        <v>32535007</v>
-      </c>
-      <c r="E7" s="37" t="inlineStr">
+        <v>79</v>
+      </c>
+      <c r="D7" s="25">
+        <v>32337077</v>
+      </c>
+      <c r="E7" s="38" t="inlineStr">
         <is>
-          <t>20261110204</t>
+          <t>20261110126</t>
         </is>
       </c>
       <c r="F7" s="16"/>
-      <c r="H7" s="16"/>
-      <c r="J7" s="16"/>
-      <c r="L7" s="16">
-        <v>4</v>
-      </c>
-      <c r="N7" s="16"/>
+      <c r="H7" s="19"/>
+      <c r="J7" s="19"/>
+      <c r="L7" s="16"/>
+      <c r="N7" s="19"/>
       <c r="O7" s="28"/>
-      <c r="P7" s="30"/>
-      <c r="Q7">
-        <v>1</v>
-      </c>
+      <c r="P7" s="32"/>
       <c r="V7" s="16"/>
       <c r="Z7" s="16"/>
     </row>
-    <row r="8" spans="1:29" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="20">
         <v>2</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>67</v>
+        <v>115</v>
       </c>
       <c r="D8" s="25">
-        <v>32753793</v>
+        <v>32624143</v>
       </c>
       <c r="E8" s="38" t="inlineStr">
         <is>
-          <t>20261110278</t>
+          <t>20261110294</t>
         </is>
       </c>
       <c r="F8" s="17"/>
-      <c r="H8" s="18"/>
-      <c r="J8" s="17"/>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8" s="17"/>
+      <c r="J8" s="17">
+        <v>2</v>
+      </c>
       <c r="L8" s="17"/>
       <c r="N8" s="17"/>
       <c r="O8" s="28"/>
       <c r="P8" s="31"/>
-      <c r="V8" s="17"/>
+      <c r="V8" s="17">
+        <v>1</v>
+      </c>
       <c r="Z8" s="17"/>
     </row>
-    <row r="9" spans="1:29" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="20">
         <v>3</v>
       </c>
-      <c r="B9" s="21" t="s">
-        <v>89</v>
+      <c r="B9" s="26" t="s">
+        <v>111</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>68</v>
+        <v>117</v>
       </c>
       <c r="D9" s="25">
-        <v>32473285</v>
+        <v>32538098</v>
       </c>
       <c r="E9" s="38" t="inlineStr">
         <is>
-          <t>20261110523</t>
+          <t>20261110623</t>
         </is>
       </c>
-      <c r="F9" s="16"/>
-      <c r="H9" s="19"/>
-      <c r="J9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="N9" s="16"/>
+      <c r="F9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="J9" s="17"/>
+      <c r="L9" s="17"/>
+      <c r="N9" s="17"/>
       <c r="O9" s="28"/>
-      <c r="P9" s="30"/>
-      <c r="V9" s="16">
-        <v>1</v>
-      </c>
-      <c r="Z9" s="16"/>
+      <c r="P9" s="31"/>
+      <c r="V9" s="17"/>
+      <c r="Z9" s="17"/>
     </row>
     <row r="10" spans="1:29" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="20">
         <v>4</v>
       </c>
-      <c r="B10" s="24" t="s">
-        <v>90</v>
+      <c r="B10" s="21" t="s">
+        <v>93</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D10" s="25">
-        <v>32235603</v>
+        <v>31821320</v>
       </c>
       <c r="E10" s="38" t="inlineStr">
         <is>
-          <t>20261110725</t>
+          <t>20261110394</t>
         </is>
       </c>
-      <c r="F10" s="17"/>
-      <c r="H10" s="17"/>
-      <c r="J10" s="18"/>
-      <c r="L10" s="17"/>
-      <c r="N10" s="17"/>
+      <c r="F10" s="16">
+        <v>1</v>
+      </c>
+      <c r="H10" s="16"/>
+      <c r="J10" s="19">
+        <v>2</v>
+      </c>
+      <c r="L10" s="16">
+        <v>2</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="N10" s="16">
+        <v>1</v>
+      </c>
       <c r="O10" s="28"/>
-      <c r="P10" s="31"/>
-      <c r="V10" s="17"/>
-      <c r="Z10" s="17"/>
+      <c r="P10" s="30"/>
+      <c r="Q10" s="29">
+        <v>3</v>
+      </c>
+      <c r="V10" s="16"/>
+      <c r="Z10" s="16"/>
     </row>
     <row r="11" spans="1:29" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="20">
         <v>5</v>
       </c>
-      <c r="B11" s="21" t="s">
-        <v>91</v>
+      <c r="B11" s="24" t="s">
+        <v>88</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D11" s="25">
-        <v>32749893</v>
+        <v>32753793</v>
       </c>
       <c r="E11" s="38" t="inlineStr">
         <is>
-          <t>20261110557</t>
+          <t>20261110278</t>
         </is>
       </c>
-      <c r="F11" s="16"/>
-      <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="H11" s="16"/>
-      <c r="J11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="N11" s="16">
-        <v>1</v>
-      </c>
+      <c r="F11" s="17"/>
+      <c r="H11" s="18"/>
+      <c r="J11" s="17"/>
+      <c r="L11" s="17"/>
+      <c r="N11" s="17"/>
       <c r="O11" s="28"/>
-      <c r="P11" s="30"/>
-      <c r="V11" s="16"/>
-      <c r="Z11" s="16"/>
-    </row>
-    <row r="12" spans="1:29" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="P11" s="31"/>
+      <c r="V11" s="17"/>
+      <c r="Z11" s="17"/>
+    </row>
+    <row r="12" spans="1:27" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="20">
         <v>6</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D12" s="25">
-        <v>32227280</v>
+        <v>32122247</v>
       </c>
       <c r="E12" s="38" t="inlineStr">
         <is>
-          <t>20261110373</t>
+          <t>20261110499</t>
         </is>
       </c>
       <c r="F12" s="17"/>
-      <c r="G12">
-        <v>1</v>
-      </c>
       <c r="H12" s="17"/>
-      <c r="J12" s="17"/>
+      <c r="J12" s="17">
+        <v>1</v>
+      </c>
       <c r="L12" s="17"/>
       <c r="N12" s="17"/>
       <c r="O12" s="28"/>
       <c r="P12" s="31"/>
-      <c r="V12" s="17">
-        <v>1</v>
-      </c>
-      <c r="Z12" s="17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:29" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="V12" s="17"/>
+      <c r="Z12" s="17"/>
+    </row>
+    <row r="13" spans="1:27" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="20">
         <v>7</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D13" s="25">
-        <v>31821320</v>
+        <v>32857188</v>
       </c>
       <c r="E13" s="38" t="inlineStr">
         <is>
-          <t>20261110394</t>
+          <t>20261110259</t>
         </is>
       </c>
       <c r="F13" s="16">
         <v>1</v>
       </c>
       <c r="H13" s="16"/>
-      <c r="J13" s="19">
-        <v>2</v>
-      </c>
-      <c r="L13" s="16">
-        <v>2</v>
-      </c>
-      <c r="M13">
-        <v>1</v>
-      </c>
-      <c r="N13" s="16">
-        <v>1</v>
-      </c>
+      <c r="J13" s="16">
+        <v>3</v>
+      </c>
+      <c r="L13" s="16"/>
+      <c r="N13" s="16"/>
       <c r="O13" s="28"/>
       <c r="P13" s="30"/>
-      <c r="Q13" s="29">
-        <v>3</v>
-      </c>
-      <c r="V13" s="16"/>
+      <c r="V13" s="16">
+        <v>1</v>
+      </c>
       <c r="Z13" s="16"/>
     </row>
     <row r="14" spans="1:29" ht="16" thickBot="1" x14ac:dyDescent="0.25">
@@ -5508,24 +5505,22 @@
         <v>8</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D14" s="25">
-        <v>36064964</v>
+        <v>32235603</v>
       </c>
       <c r="E14" s="38" t="inlineStr">
         <is>
-          <t>20261110163</t>
+          <t>20261110725</t>
         </is>
       </c>
-      <c r="F14" s="18">
-        <v>1</v>
-      </c>
+      <c r="F14" s="17"/>
       <c r="H14" s="17"/>
-      <c r="J14" s="17"/>
+      <c r="J14" s="18"/>
       <c r="L14" s="17"/>
       <c r="N14" s="17"/>
       <c r="O14" s="28"/>
@@ -5533,27 +5528,29 @@
       <c r="V14" s="17"/>
       <c r="Z14" s="17"/>
     </row>
-    <row r="15" spans="1:29" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="20">
         <v>9</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D15" s="25">
-        <v>32357635</v>
+        <v>32013622</v>
       </c>
       <c r="E15" s="38" t="inlineStr">
         <is>
-          <t>20251130204</t>
+          <t>20251110490</t>
         </is>
       </c>
-      <c r="F15" s="16"/>
-      <c r="H15" s="16"/>
-      <c r="J15" s="16"/>
+      <c r="F15" s="16">
+        <v>1</v>
+      </c>
+      <c r="H15" s="19"/>
+      <c r="J15" s="19"/>
       <c r="L15" s="16"/>
       <c r="N15" s="16"/>
       <c r="O15" s="28"/>
@@ -5561,68 +5558,68 @@
       <c r="V15" s="16"/>
       <c r="Z15" s="16"/>
     </row>
-    <row r="16" spans="1:29" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="20">
         <v>10</v>
       </c>
-      <c r="B16" s="24" t="s">
-        <v>96</v>
+      <c r="B16" s="26" t="s">
+        <v>112</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>75</v>
+        <v>118</v>
       </c>
       <c r="D16" s="25">
-        <v>30538964</v>
+        <v>32110956</v>
       </c>
       <c r="E16" s="38" t="inlineStr">
         <is>
-          <t>20261110267</t>
+          <t>20261110092</t>
         </is>
       </c>
-      <c r="F16" s="17"/>
-      <c r="H16" s="17"/>
-      <c r="J16" s="18"/>
-      <c r="L16" s="17">
-        <v>1</v>
-      </c>
-      <c r="N16" s="17"/>
+      <c r="F16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="J16" s="16"/>
+      <c r="L16" s="16"/>
+      <c r="N16" s="16"/>
       <c r="O16" s="28"/>
-      <c r="P16" s="31"/>
-      <c r="V16" s="17"/>
-      <c r="Z16" s="17"/>
-      <c r="AA16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="P16" s="30"/>
+      <c r="V16" s="16"/>
+      <c r="Z16" s="16"/>
+    </row>
+    <row r="17" spans="1:29" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="20">
         <v>11</v>
       </c>
-      <c r="B17" s="21" t="s">
-        <v>97</v>
+      <c r="B17" s="24" t="s">
+        <v>92</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D17" s="25">
-        <v>32348335</v>
+        <v>32227280</v>
       </c>
       <c r="E17" s="38" t="inlineStr">
         <is>
-          <t>20261110006</t>
+          <t>20261110373</t>
         </is>
       </c>
-      <c r="F17" s="16">
-        <v>1</v>
-      </c>
-      <c r="H17" s="16"/>
-      <c r="J17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="N17" s="16"/>
+      <c r="F17" s="17"/>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17" s="17"/>
+      <c r="J17" s="17"/>
+      <c r="L17" s="17"/>
+      <c r="N17" s="17"/>
       <c r="O17" s="28"/>
-      <c r="P17" s="30"/>
-      <c r="V17" s="16"/>
-      <c r="Z17" s="16"/>
+      <c r="P17" s="31"/>
+      <c r="V17" s="17">
+        <v>1</v>
+      </c>
+      <c r="Z17" s="17">
+        <v>1</v>
+      </c>
     </row>
     <row r="18" spans="1:27" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="20">
@@ -5657,24 +5654,22 @@
         <v>13</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D19" s="25">
-        <v>32013622</v>
+        <v>34002480</v>
       </c>
       <c r="E19" s="38" t="inlineStr">
         <is>
-          <t>20251110490</t>
+          <t>20261110653</t>
         </is>
       </c>
-      <c r="F19" s="16">
-        <v>1</v>
-      </c>
-      <c r="H19" s="19"/>
-      <c r="J19" s="19"/>
+      <c r="F19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="J19" s="16"/>
       <c r="L19" s="16"/>
       <c r="N19" s="16"/>
       <c r="O19" s="28"/>
@@ -5713,64 +5708,65 @@
       <c r="V20" s="17"/>
       <c r="Z20" s="17"/>
     </row>
-    <row r="21" spans="1:27" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:29" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="20">
         <v>15</v>
       </c>
-      <c r="B21" s="21" t="s">
-        <v>101</v>
+      <c r="B21" s="24" t="s">
+        <v>96</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D21" s="25">
-        <v>32337077</v>
+        <v>30538964</v>
       </c>
       <c r="E21" s="38" t="inlineStr">
         <is>
-          <t>20261110126</t>
+          <t>20261110267</t>
         </is>
       </c>
-      <c r="F21" s="16"/>
-      <c r="H21" s="19"/>
-      <c r="J21" s="19"/>
-      <c r="L21" s="16"/>
-      <c r="N21" s="19"/>
+      <c r="F21" s="17"/>
+      <c r="H21" s="17"/>
+      <c r="J21" s="18"/>
+      <c r="L21" s="17">
+        <v>1</v>
+      </c>
+      <c r="N21" s="17"/>
       <c r="O21" s="28"/>
-      <c r="P21" s="32"/>
-      <c r="V21" s="16"/>
-      <c r="Z21" s="16"/>
-    </row>
-    <row r="22" spans="1:27" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="P21" s="31"/>
+      <c r="V21" s="17"/>
+      <c r="Z21" s="17"/>
+      <c r="AA21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:26" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="20">
         <v>16</v>
       </c>
-      <c r="B22" s="24" t="s">
-        <v>102</v>
+      <c r="B22" s="26" t="s">
+        <v>113</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>80</v>
-      </c>
-      <c r="D22" s="25">
-        <v>32348512</v>
+        <v>119</v>
+      </c>
+      <c r="D22" s="27">
+        <v>30774515</v>
       </c>
       <c r="E22" s="38" t="inlineStr">
         <is>
-          <t>20261110130</t>
+          <t>20251130180</t>
         </is>
       </c>
-      <c r="F22" s="17">
-        <v>1</v>
-      </c>
+      <c r="F22" s="17"/>
       <c r="H22" s="17"/>
-      <c r="J22" s="18"/>
+      <c r="J22" s="17"/>
       <c r="L22" s="17"/>
-      <c r="N22" s="18"/>
+      <c r="N22" s="17"/>
       <c r="O22" s="28"/>
       <c r="P22" s="31"/>
-      <c r="V22" s="17">
-        <v>1</v>
-      </c>
+      <c r="V22" s="17"/>
       <c r="Z22" s="17"/>
     </row>
     <row r="23" spans="1:27" ht="16" thickBot="1" x14ac:dyDescent="0.25">
@@ -5778,29 +5774,22 @@
         <v>17</v>
       </c>
       <c r="B23" s="21" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C23" s="22" t="s">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="D23" s="25">
-        <v>32226530</v>
+        <v>31873213</v>
       </c>
       <c r="E23" s="38" t="inlineStr">
         <is>
-          <t>20261110202</t>
+          <t>20241110461</t>
         </is>
       </c>
-      <c r="F23" s="16">
-        <v>1</v>
-      </c>
-      <c r="H23" s="19"/>
-      <c r="J23" s="19">
-        <v>2</v>
-      </c>
-      <c r="K23">
-        <v>1</v>
-      </c>
+      <c r="F23" s="16"/>
+      <c r="H23" s="16"/>
+      <c r="J23" s="16"/>
       <c r="L23" s="16"/>
       <c r="N23" s="16"/>
       <c r="O23" s="28"/>
@@ -5808,61 +5797,61 @@
       <c r="V23" s="16"/>
       <c r="Z23" s="16"/>
     </row>
-    <row r="24" spans="1:27" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="20">
         <v>18</v>
       </c>
-      <c r="B24" s="24" t="s">
-        <v>104</v>
+      <c r="B24" s="26" t="s">
+        <v>110</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="D24" s="25">
-        <v>31873764</v>
+        <v>32504495</v>
       </c>
       <c r="E24" s="38" t="inlineStr">
         <is>
-          <t>20251110157</t>
+          <t>20261110285</t>
         </is>
       </c>
-      <c r="F24" s="17"/>
-      <c r="H24" s="17"/>
-      <c r="J24" s="17"/>
-      <c r="K24">
-        <v>1</v>
-      </c>
-      <c r="L24" s="17">
-        <v>1</v>
-      </c>
-      <c r="M24">
+      <c r="F24" s="16">
+        <v>1</v>
+      </c>
+      <c r="H24" s="16"/>
+      <c r="J24" s="16">
         <v>3</v>
       </c>
-      <c r="N24" s="17"/>
+      <c r="L24" s="16"/>
+      <c r="N24" s="16"/>
       <c r="O24" s="28"/>
-      <c r="P24" s="31"/>
-      <c r="V24" s="17"/>
-      <c r="Z24" s="17"/>
+      <c r="P24" s="30"/>
+      <c r="V24" s="16">
+        <v>1</v>
+      </c>
+      <c r="Z24" s="16"/>
     </row>
     <row r="25" spans="1:27" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="20">
         <v>19</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C25" s="22" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="D25" s="25">
-        <v>32396833</v>
+        <v>32348335</v>
       </c>
       <c r="E25" s="38" t="inlineStr">
         <is>
-          <t>20261110444</t>
+          <t>20261110006</t>
         </is>
       </c>
-      <c r="F25" s="16"/>
+      <c r="F25" s="16">
+        <v>1</v>
+      </c>
       <c r="H25" s="16"/>
       <c r="J25" s="16"/>
       <c r="L25" s="16"/>
@@ -5871,127 +5860,134 @@
       <c r="P25" s="30"/>
       <c r="V25" s="16"/>
       <c r="Z25" s="16"/>
-      <c r="AA25">
-        <v>1</v>
-      </c>
     </row>
     <row r="26" spans="1:27" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="20">
         <v>20</v>
       </c>
       <c r="B26" s="24" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C26" s="22" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D26" s="25">
-        <v>32292306</v>
+        <v>31873764</v>
       </c>
       <c r="E26" s="38" t="inlineStr">
         <is>
-          <t>20261110337</t>
+          <t>20251110157</t>
         </is>
       </c>
       <c r="F26" s="17"/>
       <c r="H26" s="17"/>
       <c r="J26" s="17"/>
+      <c r="K26">
+        <v>1</v>
+      </c>
       <c r="L26" s="17">
         <v>1</v>
+      </c>
+      <c r="M26">
+        <v>3</v>
       </c>
       <c r="N26" s="17"/>
       <c r="O26" s="28"/>
       <c r="P26" s="31"/>
       <c r="V26" s="17"/>
       <c r="Z26" s="17"/>
-      <c r="AA26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:27" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:29" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="20">
         <v>21</v>
       </c>
       <c r="B27" s="21" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="C27" s="22" t="s">
-        <v>114</v>
+        <v>68</v>
       </c>
       <c r="D27" s="25">
-        <v>31873213</v>
+        <v>32473285</v>
       </c>
       <c r="E27" s="38" t="inlineStr">
         <is>
-          <t>20241110461</t>
+          <t>20261110523</t>
         </is>
       </c>
       <c r="F27" s="16"/>
-      <c r="H27" s="16"/>
+      <c r="H27" s="19"/>
       <c r="J27" s="16"/>
       <c r="L27" s="16"/>
       <c r="N27" s="16"/>
       <c r="O27" s="28"/>
       <c r="P27" s="30"/>
-      <c r="V27" s="16"/>
+      <c r="V27" s="16">
+        <v>1</v>
+      </c>
       <c r="Z27" s="16"/>
     </row>
-    <row r="28" spans="1:27" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:29" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="20">
         <v>22</v>
       </c>
-      <c r="B28" s="24" t="s">
-        <v>95</v>
+      <c r="B28" s="21" t="s">
+        <v>87</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="D28" s="25">
-        <v>32520003</v>
-      </c>
-      <c r="E28" s="38" t="inlineStr">
+        <v>66</v>
+      </c>
+      <c r="D28" s="23">
+        <v>32535007</v>
+      </c>
+      <c r="E28" s="37" t="inlineStr">
         <is>
-          <t>20261110687</t>
+          <t>20261110204</t>
         </is>
       </c>
-      <c r="F28" s="17">
-        <v>1</v>
-      </c>
-      <c r="G28">
-        <v>1</v>
-      </c>
-      <c r="H28" s="18"/>
-      <c r="J28" s="18"/>
-      <c r="L28" s="17"/>
-      <c r="N28" s="18"/>
+      <c r="F28" s="16"/>
+      <c r="H28" s="16"/>
+      <c r="J28" s="16"/>
+      <c r="L28" s="16">
+        <v>4</v>
+      </c>
+      <c r="N28" s="16"/>
       <c r="O28" s="28"/>
-      <c r="P28" s="33"/>
-      <c r="V28" s="17"/>
-      <c r="Z28" s="17"/>
-    </row>
-    <row r="29" spans="1:27" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="P28" s="30"/>
+      <c r="Q28">
+        <v>1</v>
+      </c>
+      <c r="V28" s="16"/>
+      <c r="Z28" s="16"/>
+    </row>
+    <row r="29" spans="1:29" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="20">
         <v>23</v>
       </c>
       <c r="B29" s="21" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="C29" s="22" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D29" s="25">
-        <v>34002480</v>
+        <v>32749893</v>
       </c>
       <c r="E29" s="38" t="inlineStr">
         <is>
-          <t>20261110653</t>
+          <t>20261110557</t>
         </is>
       </c>
       <c r="F29" s="16"/>
+      <c r="G29">
+        <v>1</v>
+      </c>
       <c r="H29" s="16"/>
       <c r="J29" s="16"/>
       <c r="L29" s="16"/>
-      <c r="N29" s="16"/>
+      <c r="N29" s="16">
+        <v>1</v>
+      </c>
       <c r="O29" s="28"/>
       <c r="P29" s="30"/>
       <c r="V29" s="16"/>
@@ -6002,153 +5998,151 @@
         <v>24</v>
       </c>
       <c r="B30" s="24" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C30" s="22" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="D30" s="25">
-        <v>32122247</v>
+        <v>32292306</v>
       </c>
       <c r="E30" s="38" t="inlineStr">
         <is>
-          <t>20261110499</t>
+          <t>20261110337</t>
         </is>
       </c>
       <c r="F30" s="17"/>
       <c r="H30" s="17"/>
-      <c r="J30" s="17">
-        <v>1</v>
-      </c>
-      <c r="L30" s="17"/>
+      <c r="J30" s="17"/>
+      <c r="L30" s="17">
+        <v>1</v>
+      </c>
       <c r="N30" s="17"/>
       <c r="O30" s="28"/>
       <c r="P30" s="31"/>
       <c r="V30" s="17"/>
       <c r="Z30" s="17"/>
+      <c r="AA30">
+        <v>1</v>
+      </c>
     </row>
     <row r="31" spans="1:27" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="20">
         <v>25</v>
       </c>
-      <c r="B31" s="21" t="s">
+      <c r="B31" s="24" t="s">
         <v>95</v>
       </c>
       <c r="C31" s="22" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="D31" s="25">
-        <v>32857188</v>
+        <v>32520003</v>
       </c>
       <c r="E31" s="38" t="inlineStr">
         <is>
-          <t>20261110259</t>
+          <t>20261110687</t>
         </is>
       </c>
-      <c r="F31" s="16">
-        <v>1</v>
-      </c>
-      <c r="H31" s="16"/>
-      <c r="J31" s="16">
-        <v>3</v>
-      </c>
-      <c r="L31" s="16"/>
-      <c r="N31" s="16"/>
+      <c r="F31" s="17">
+        <v>1</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+      <c r="H31" s="18"/>
+      <c r="J31" s="18"/>
+      <c r="L31" s="17"/>
+      <c r="N31" s="18"/>
       <c r="O31" s="28"/>
-      <c r="P31" s="30"/>
-      <c r="V31" s="16">
-        <v>1</v>
-      </c>
-      <c r="Z31" s="16"/>
-    </row>
-    <row r="32" spans="1:27" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="P31" s="33"/>
+      <c r="V31" s="17"/>
+      <c r="Z31" s="17"/>
+    </row>
+    <row r="32" spans="1:29" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="20">
         <v>26</v>
       </c>
-      <c r="B32" s="24" t="s">
-        <v>109</v>
+      <c r="B32" s="21" t="s">
+        <v>95</v>
       </c>
       <c r="C32" s="22" t="s">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="D32" s="25">
-        <v>32624143</v>
+        <v>32357635</v>
       </c>
       <c r="E32" s="38" t="inlineStr">
         <is>
-          <t>20261110294</t>
+          <t>20251130204</t>
         </is>
       </c>
-      <c r="F32" s="17"/>
-      <c r="G32">
-        <v>1</v>
-      </c>
-      <c r="H32" s="17"/>
-      <c r="J32" s="17">
-        <v>2</v>
-      </c>
-      <c r="L32" s="17"/>
-      <c r="N32" s="17"/>
+      <c r="F32" s="16"/>
+      <c r="H32" s="16"/>
+      <c r="J32" s="16"/>
+      <c r="L32" s="16"/>
+      <c r="N32" s="16"/>
       <c r="O32" s="28"/>
-      <c r="P32" s="31"/>
-      <c r="V32" s="17">
-        <v>1</v>
-      </c>
-      <c r="Z32" s="17"/>
-    </row>
-    <row r="33" spans="1:26" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="P32" s="30"/>
+      <c r="V32" s="16"/>
+      <c r="Z32" s="16"/>
+    </row>
+    <row r="33" spans="1:27" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="20">
         <v>27</v>
       </c>
-      <c r="B33" s="26" t="s">
-        <v>110</v>
+      <c r="B33" s="21" t="s">
+        <v>103</v>
       </c>
       <c r="C33" s="22" t="s">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="D33" s="25">
-        <v>32504495</v>
+        <v>32226530</v>
       </c>
       <c r="E33" s="38" t="inlineStr">
         <is>
-          <t>20261110285</t>
+          <t>20261110202</t>
         </is>
       </c>
       <c r="F33" s="16">
         <v>1</v>
       </c>
-      <c r="H33" s="16"/>
-      <c r="J33" s="16">
-        <v>3</v>
+      <c r="H33" s="19"/>
+      <c r="J33" s="19">
+        <v>2</v>
+      </c>
+      <c r="K33">
+        <v>1</v>
       </c>
       <c r="L33" s="16"/>
       <c r="N33" s="16"/>
       <c r="O33" s="28"/>
       <c r="P33" s="30"/>
-      <c r="V33" s="16">
-        <v>1</v>
-      </c>
+      <c r="V33" s="16"/>
       <c r="Z33" s="16"/>
     </row>
-    <row r="34" spans="1:26" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:29" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A34" s="20">
         <v>28</v>
       </c>
-      <c r="B34" s="26" t="s">
-        <v>111</v>
+      <c r="B34" s="24" t="s">
+        <v>94</v>
       </c>
       <c r="C34" s="22" t="s">
-        <v>117</v>
+        <v>73</v>
       </c>
       <c r="D34" s="25">
-        <v>32538098</v>
+        <v>36064964</v>
       </c>
       <c r="E34" s="38" t="inlineStr">
         <is>
-          <t>20261110623</t>
+          <t>20261110163</t>
         </is>
       </c>
-      <c r="F34" s="17"/>
+      <c r="F34" s="18">
+        <v>1</v>
+      </c>
       <c r="H34" s="17"/>
       <c r="J34" s="17"/>
       <c r="L34" s="17"/>
@@ -6158,61 +6152,68 @@
       <c r="V34" s="17"/>
       <c r="Z34" s="17"/>
     </row>
-    <row r="35" spans="1:26" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:27" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="20">
         <v>29</v>
       </c>
-      <c r="B35" s="26" t="s">
-        <v>112</v>
+      <c r="B35" s="24" t="s">
+        <v>102</v>
       </c>
       <c r="C35" s="22" t="s">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="D35" s="25">
-        <v>32110956</v>
+        <v>32348512</v>
       </c>
       <c r="E35" s="38" t="inlineStr">
         <is>
-          <t>20261110092</t>
+          <t>20261110130</t>
         </is>
       </c>
-      <c r="F35" s="16"/>
-      <c r="H35" s="16"/>
-      <c r="J35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="N35" s="16"/>
+      <c r="F35" s="17">
+        <v>1</v>
+      </c>
+      <c r="H35" s="17"/>
+      <c r="J35" s="18"/>
+      <c r="L35" s="17"/>
+      <c r="N35" s="18"/>
       <c r="O35" s="28"/>
-      <c r="P35" s="30"/>
-      <c r="V35" s="16"/>
-      <c r="Z35" s="16"/>
-    </row>
-    <row r="36" spans="1:26" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="P35" s="31"/>
+      <c r="V35" s="17">
+        <v>1</v>
+      </c>
+      <c r="Z35" s="17"/>
+    </row>
+    <row r="36" spans="1:27" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="20">
         <v>30</v>
       </c>
-      <c r="B36" s="26" t="s">
-        <v>113</v>
+      <c r="B36" s="21" t="s">
+        <v>105</v>
       </c>
       <c r="C36" s="22" t="s">
-        <v>119</v>
-      </c>
-      <c r="D36" s="27">
-        <v>30774515</v>
+        <v>83</v>
+      </c>
+      <c r="D36" s="25">
+        <v>32396833</v>
       </c>
       <c r="E36" s="38" t="inlineStr">
         <is>
-          <t>20251130180</t>
+          <t>20261110444</t>
         </is>
       </c>
-      <c r="F36" s="17"/>
-      <c r="H36" s="17"/>
-      <c r="J36" s="17"/>
-      <c r="L36" s="17"/>
-      <c r="N36" s="17"/>
+      <c r="F36" s="16"/>
+      <c r="H36" s="16"/>
+      <c r="J36" s="16"/>
+      <c r="L36" s="16"/>
+      <c r="N36" s="16"/>
       <c r="O36" s="28"/>
-      <c r="P36" s="31"/>
-      <c r="V36" s="17"/>
-      <c r="Z36" s="17"/>
+      <c r="P36" s="30"/>
+      <c r="V36" s="16"/>
+      <c r="Z36" s="16"/>
+      <c r="AA36">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -6236,4 +6237,360 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">semana</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dia_sesion</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tema</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tipo_sesion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>4</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>4</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>5</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">repaso</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>5</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>6</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>6</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>7</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sin_clase</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>7</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>8</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>8</v>
+      </c>
+      <c r="B17">
+        <v>2</v>
+      </c>
+      <c r="C17">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>9</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>9</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>10</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>10</v>
+      </c>
+      <c r="B21">
+        <v>2</v>
+      </c>
+      <c r="C21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>11</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>11</v>
+      </c>
+      <c r="B23">
+        <v>2</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>12</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">administrativa</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>12</v>
+      </c>
+      <c r="B25">
+        <v>2</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">administrativa</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nota:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tema = código del catálogo de la asignatura. Si la sesión no cubre contenido nuevo: tema = 0 y tipo_sesion indica la causa (evaluacion, repaso, sin_clase, administrativa). Si tema &gt; 0 la sesión es de contenido y tipo_sesion queda vacío.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>